--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441334</v>
+        <v>113441377</v>
       </c>
       <c r="B2" t="n">
-        <v>91302</v>
+        <v>91306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775924</v>
+        <v>775928</v>
       </c>
       <c r="R2" t="n">
-        <v>7216402</v>
+        <v>7216628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441236</v>
+        <v>113441334</v>
       </c>
       <c r="B3" t="n">
-        <v>91282</v>
+        <v>91318</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775939</v>
+        <v>775924</v>
       </c>
       <c r="R3" t="n">
-        <v>7216449</v>
+        <v>7216402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441203</v>
+        <v>113441200</v>
       </c>
       <c r="B4" t="n">
-        <v>91294</v>
+        <v>91349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775972</v>
+        <v>775838</v>
       </c>
       <c r="R4" t="n">
-        <v>7216501</v>
+        <v>7216566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441385</v>
+        <v>113441196</v>
       </c>
       <c r="B5" t="n">
-        <v>91284</v>
+        <v>91292</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775948</v>
+        <v>775933</v>
       </c>
       <c r="R5" t="n">
-        <v>7216449</v>
+        <v>7216437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441367</v>
+        <v>113441204</v>
       </c>
       <c r="B6" t="n">
-        <v>88654</v>
+        <v>91310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775936</v>
+        <v>775964</v>
       </c>
       <c r="R6" t="n">
-        <v>7216436</v>
+        <v>7216510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441322</v>
+        <v>113441317</v>
       </c>
       <c r="B7" t="n">
-        <v>91294</v>
+        <v>91349</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775914</v>
+        <v>776019</v>
       </c>
       <c r="R7" t="n">
-        <v>7216634</v>
+        <v>7216574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441318</v>
+        <v>113441236</v>
       </c>
       <c r="B8" t="n">
-        <v>91333</v>
+        <v>91298</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775838</v>
+        <v>775939</v>
       </c>
       <c r="R8" t="n">
-        <v>7216566</v>
+        <v>7216449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441321</v>
+        <v>113441203</v>
       </c>
       <c r="B9" t="n">
-        <v>91294</v>
+        <v>91310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775964</v>
+        <v>775972</v>
       </c>
       <c r="R9" t="n">
-        <v>7216510</v>
+        <v>7216501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441206</v>
+        <v>113441319</v>
       </c>
       <c r="B10" t="n">
-        <v>91294</v>
+        <v>91350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775841</v>
+        <v>775880</v>
       </c>
       <c r="R10" t="n">
-        <v>7216570</v>
+        <v>7216579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441314</v>
+        <v>113441385</v>
       </c>
       <c r="B11" t="n">
-        <v>91276</v>
+        <v>91300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775933</v>
+        <v>775948</v>
       </c>
       <c r="R11" t="n">
-        <v>7216437</v>
+        <v>7216449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441377</v>
+        <v>113441323</v>
       </c>
       <c r="B12" t="n">
-        <v>91290</v>
+        <v>91310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775928</v>
+        <v>775841</v>
       </c>
       <c r="R12" t="n">
-        <v>7216628</v>
+        <v>7216570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441319</v>
+        <v>113441205</v>
       </c>
       <c r="B13" t="n">
-        <v>91334</v>
+        <v>91310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775880</v>
+        <v>775914</v>
       </c>
       <c r="R13" t="n">
-        <v>7216579</v>
+        <v>7216634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441199</v>
+        <v>113441248</v>
       </c>
       <c r="B14" t="n">
-        <v>91333</v>
+        <v>88670</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5448</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776019</v>
+        <v>775936</v>
       </c>
       <c r="R14" t="n">
-        <v>7216574</v>
+        <v>7216436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441377</v>
+        <v>113441314</v>
       </c>
       <c r="B2" t="n">
-        <v>91306</v>
+        <v>91292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775928</v>
+        <v>775933</v>
       </c>
       <c r="R2" t="n">
-        <v>7216628</v>
+        <v>7216437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441334</v>
+        <v>113441200</v>
       </c>
       <c r="B3" t="n">
-        <v>91318</v>
+        <v>91349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775924</v>
+        <v>775838</v>
       </c>
       <c r="R3" t="n">
-        <v>7216402</v>
+        <v>7216566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441200</v>
+        <v>113441258</v>
       </c>
       <c r="B4" t="n">
-        <v>91349</v>
+        <v>91306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775838</v>
+        <v>775928</v>
       </c>
       <c r="R4" t="n">
-        <v>7216566</v>
+        <v>7216628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441196</v>
+        <v>113441216</v>
       </c>
       <c r="B5" t="n">
-        <v>91292</v>
+        <v>91318</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775933</v>
+        <v>775924</v>
       </c>
       <c r="R5" t="n">
-        <v>7216437</v>
+        <v>7216402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441204</v>
+        <v>113441199</v>
       </c>
       <c r="B6" t="n">
-        <v>91310</v>
+        <v>91349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775964</v>
+        <v>776019</v>
       </c>
       <c r="R6" t="n">
-        <v>7216510</v>
+        <v>7216574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441317</v>
+        <v>113441321</v>
       </c>
       <c r="B7" t="n">
-        <v>91349</v>
+        <v>91310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776019</v>
+        <v>775964</v>
       </c>
       <c r="R7" t="n">
-        <v>7216574</v>
+        <v>7216510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441236</v>
+        <v>113441203</v>
       </c>
       <c r="B8" t="n">
-        <v>91298</v>
+        <v>91310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775939</v>
+        <v>775972</v>
       </c>
       <c r="R8" t="n">
-        <v>7216449</v>
+        <v>7216501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441203</v>
+        <v>113441206</v>
       </c>
       <c r="B9" t="n">
         <v>91310</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775972</v>
+        <v>775841</v>
       </c>
       <c r="R9" t="n">
-        <v>7216501</v>
+        <v>7216570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441319</v>
+        <v>113441385</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775880</v>
+        <v>775948</v>
       </c>
       <c r="R10" t="n">
-        <v>7216579</v>
+        <v>7216449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441385</v>
+        <v>113441367</v>
       </c>
       <c r="B11" t="n">
-        <v>91300</v>
+        <v>88670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775948</v>
+        <v>775936</v>
       </c>
       <c r="R11" t="n">
-        <v>7216449</v>
+        <v>7216436</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441323</v>
+        <v>113441201</v>
       </c>
       <c r="B12" t="n">
-        <v>91310</v>
+        <v>91350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775841</v>
+        <v>775880</v>
       </c>
       <c r="R12" t="n">
-        <v>7216570</v>
+        <v>7216579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441248</v>
+        <v>113441236</v>
       </c>
       <c r="B14" t="n">
-        <v>88670</v>
+        <v>91298</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775936</v>
+        <v>775939</v>
       </c>
       <c r="R14" t="n">
-        <v>7216436</v>
+        <v>7216449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441314</v>
+        <v>113441216</v>
       </c>
       <c r="B2" t="n">
-        <v>91292</v>
+        <v>91330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775933</v>
+        <v>775924</v>
       </c>
       <c r="R2" t="n">
-        <v>7216437</v>
+        <v>7216402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441200</v>
+        <v>113441206</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>91322</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775838</v>
+        <v>775841</v>
       </c>
       <c r="R3" t="n">
-        <v>7216566</v>
+        <v>7216570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441258</v>
+        <v>113441205</v>
       </c>
       <c r="B4" t="n">
-        <v>91306</v>
+        <v>91322</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775928</v>
+        <v>775914</v>
       </c>
       <c r="R4" t="n">
-        <v>7216628</v>
+        <v>7216634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441216</v>
+        <v>113441248</v>
       </c>
       <c r="B5" t="n">
-        <v>91318</v>
+        <v>88682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775924</v>
+        <v>775936</v>
       </c>
       <c r="R5" t="n">
-        <v>7216402</v>
+        <v>7216436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441199</v>
+        <v>113441355</v>
       </c>
       <c r="B6" t="n">
-        <v>91349</v>
+        <v>91310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776019</v>
+        <v>775939</v>
       </c>
       <c r="R6" t="n">
-        <v>7216574</v>
+        <v>7216449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441321</v>
+        <v>113441258</v>
       </c>
       <c r="B7" t="n">
-        <v>91310</v>
+        <v>91318</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775964</v>
+        <v>775928</v>
       </c>
       <c r="R7" t="n">
-        <v>7216510</v>
+        <v>7216628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441203</v>
+        <v>113441385</v>
       </c>
       <c r="B8" t="n">
-        <v>91310</v>
+        <v>91312</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775972</v>
+        <v>775948</v>
       </c>
       <c r="R8" t="n">
-        <v>7216501</v>
+        <v>7216449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441206</v>
+        <v>113441314</v>
       </c>
       <c r="B9" t="n">
-        <v>91310</v>
+        <v>91304</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775841</v>
+        <v>775933</v>
       </c>
       <c r="R9" t="n">
-        <v>7216570</v>
+        <v>7216437</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441385</v>
+        <v>113441317</v>
       </c>
       <c r="B10" t="n">
-        <v>91300</v>
+        <v>91361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775948</v>
+        <v>776019</v>
       </c>
       <c r="R10" t="n">
-        <v>7216449</v>
+        <v>7216574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441367</v>
+        <v>113441318</v>
       </c>
       <c r="B11" t="n">
-        <v>88670</v>
+        <v>91361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775936</v>
+        <v>775838</v>
       </c>
       <c r="R11" t="n">
-        <v>7216436</v>
+        <v>7216566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441201</v>
+        <v>113441204</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91322</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775880</v>
+        <v>775964</v>
       </c>
       <c r="R12" t="n">
-        <v>7216579</v>
+        <v>7216510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441205</v>
+        <v>113441201</v>
       </c>
       <c r="B13" t="n">
-        <v>91310</v>
+        <v>91362</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775914</v>
+        <v>775880</v>
       </c>
       <c r="R13" t="n">
-        <v>7216634</v>
+        <v>7216579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441236</v>
+        <v>113441203</v>
       </c>
       <c r="B14" t="n">
-        <v>91298</v>
+        <v>91322</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775939</v>
+        <v>775972</v>
       </c>
       <c r="R14" t="n">
-        <v>7216449</v>
+        <v>7216501</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441216</v>
+        <v>113441320</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>91322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775924</v>
+        <v>775972</v>
       </c>
       <c r="R2" t="n">
-        <v>7216402</v>
+        <v>7216501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441206</v>
+        <v>113441318</v>
       </c>
       <c r="B3" t="n">
-        <v>91322</v>
+        <v>91361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775841</v>
+        <v>775838</v>
       </c>
       <c r="R3" t="n">
-        <v>7216570</v>
+        <v>7216566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441205</v>
+        <v>113441355</v>
       </c>
       <c r="B4" t="n">
-        <v>91322</v>
+        <v>91310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775914</v>
+        <v>775939</v>
       </c>
       <c r="R4" t="n">
-        <v>7216634</v>
+        <v>7216449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441248</v>
+        <v>113441323</v>
       </c>
       <c r="B5" t="n">
-        <v>88682</v>
+        <v>91322</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775936</v>
+        <v>775841</v>
       </c>
       <c r="R5" t="n">
-        <v>7216436</v>
+        <v>7216570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441355</v>
+        <v>113441314</v>
       </c>
       <c r="B6" t="n">
-        <v>91310</v>
+        <v>91304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775939</v>
+        <v>775933</v>
       </c>
       <c r="R6" t="n">
-        <v>7216449</v>
+        <v>7216437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441258</v>
+        <v>113441319</v>
       </c>
       <c r="B7" t="n">
-        <v>91318</v>
+        <v>91362</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775928</v>
+        <v>775880</v>
       </c>
       <c r="R7" t="n">
-        <v>7216628</v>
+        <v>7216579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441385</v>
+        <v>113441199</v>
       </c>
       <c r="B8" t="n">
-        <v>91312</v>
+        <v>91361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775948</v>
+        <v>776019</v>
       </c>
       <c r="R8" t="n">
-        <v>7216449</v>
+        <v>7216574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441314</v>
+        <v>113441321</v>
       </c>
       <c r="B9" t="n">
-        <v>91304</v>
+        <v>91322</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775933</v>
+        <v>775964</v>
       </c>
       <c r="R9" t="n">
-        <v>7216437</v>
+        <v>7216510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441317</v>
+        <v>113441216</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776019</v>
+        <v>775924</v>
       </c>
       <c r="R10" t="n">
-        <v>7216574</v>
+        <v>7216402</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441318</v>
+        <v>113441248</v>
       </c>
       <c r="B11" t="n">
-        <v>91361</v>
+        <v>88682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775838</v>
+        <v>775936</v>
       </c>
       <c r="R11" t="n">
-        <v>7216566</v>
+        <v>7216436</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441204</v>
+        <v>113441258</v>
       </c>
       <c r="B12" t="n">
-        <v>91322</v>
+        <v>91318</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775964</v>
+        <v>775928</v>
       </c>
       <c r="R12" t="n">
-        <v>7216510</v>
+        <v>7216628</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441201</v>
+        <v>113441322</v>
       </c>
       <c r="B13" t="n">
-        <v>91362</v>
+        <v>91322</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775880</v>
+        <v>775914</v>
       </c>
       <c r="R13" t="n">
-        <v>7216579</v>
+        <v>7216634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441203</v>
+        <v>113441385</v>
       </c>
       <c r="B14" t="n">
-        <v>91322</v>
+        <v>91312</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775972</v>
+        <v>775948</v>
       </c>
       <c r="R14" t="n">
-        <v>7216501</v>
+        <v>7216449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441320</v>
+        <v>113441266</v>
       </c>
       <c r="B2" t="n">
-        <v>91322</v>
+        <v>91334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775972</v>
+        <v>775948</v>
       </c>
       <c r="R2" t="n">
-        <v>7216501</v>
+        <v>7216449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441318</v>
+        <v>113441317</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775838</v>
+        <v>776019</v>
       </c>
       <c r="R3" t="n">
-        <v>7216566</v>
+        <v>7216574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441355</v>
+        <v>113441322</v>
       </c>
       <c r="B4" t="n">
-        <v>91310</v>
+        <v>91344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775939</v>
+        <v>775914</v>
       </c>
       <c r="R4" t="n">
-        <v>7216449</v>
+        <v>7216634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441323</v>
+        <v>113441367</v>
       </c>
       <c r="B5" t="n">
-        <v>91322</v>
+        <v>88704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775841</v>
+        <v>775936</v>
       </c>
       <c r="R5" t="n">
-        <v>7216570</v>
+        <v>7216436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441314</v>
+        <v>113441355</v>
       </c>
       <c r="B6" t="n">
-        <v>91304</v>
+        <v>91332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775933</v>
+        <v>775939</v>
       </c>
       <c r="R6" t="n">
-        <v>7216437</v>
+        <v>7216449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>113441319</v>
       </c>
       <c r="B7" t="n">
-        <v>91362</v>
+        <v>91384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441199</v>
+        <v>113441206</v>
       </c>
       <c r="B8" t="n">
-        <v>91361</v>
+        <v>91344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776019</v>
+        <v>775841</v>
       </c>
       <c r="R8" t="n">
-        <v>7216574</v>
+        <v>7216570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441321</v>
+        <v>113441200</v>
       </c>
       <c r="B9" t="n">
-        <v>91322</v>
+        <v>91383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775964</v>
+        <v>775838</v>
       </c>
       <c r="R9" t="n">
-        <v>7216510</v>
+        <v>7216566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441216</v>
+        <v>113441314</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775924</v>
+        <v>775933</v>
       </c>
       <c r="R10" t="n">
-        <v>7216402</v>
+        <v>7216437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441248</v>
+        <v>113441320</v>
       </c>
       <c r="B11" t="n">
-        <v>88682</v>
+        <v>91344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775936</v>
+        <v>775972</v>
       </c>
       <c r="R11" t="n">
-        <v>7216436</v>
+        <v>7216501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441258</v>
+        <v>113441377</v>
       </c>
       <c r="B12" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441322</v>
+        <v>113441321</v>
       </c>
       <c r="B13" t="n">
-        <v>91322</v>
+        <v>91344</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775914</v>
+        <v>775964</v>
       </c>
       <c r="R13" t="n">
-        <v>7216634</v>
+        <v>7216510</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441385</v>
+        <v>113441334</v>
       </c>
       <c r="B14" t="n">
-        <v>91312</v>
+        <v>91352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775948</v>
+        <v>775924</v>
       </c>
       <c r="R14" t="n">
-        <v>7216449</v>
+        <v>7216402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441266</v>
+        <v>113441322</v>
       </c>
       <c r="B2" t="n">
-        <v>91334</v>
+        <v>91348</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775948</v>
+        <v>775914</v>
       </c>
       <c r="R2" t="n">
-        <v>7216449</v>
+        <v>7216634</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441317</v>
+        <v>113441201</v>
       </c>
       <c r="B3" t="n">
-        <v>91383</v>
+        <v>91388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776019</v>
+        <v>775880</v>
       </c>
       <c r="R3" t="n">
-        <v>7216574</v>
+        <v>7216579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441322</v>
+        <v>113441320</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775914</v>
+        <v>775972</v>
       </c>
       <c r="R4" t="n">
-        <v>7216634</v>
+        <v>7216501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441367</v>
+        <v>113441323</v>
       </c>
       <c r="B5" t="n">
-        <v>88704</v>
+        <v>91348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775936</v>
+        <v>775841</v>
       </c>
       <c r="R5" t="n">
-        <v>7216436</v>
+        <v>7216570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441355</v>
+        <v>113441321</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>91348</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775939</v>
+        <v>775964</v>
       </c>
       <c r="R6" t="n">
-        <v>7216449</v>
+        <v>7216510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441319</v>
+        <v>113441318</v>
       </c>
       <c r="B7" t="n">
-        <v>91384</v>
+        <v>91387</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775880</v>
+        <v>775838</v>
       </c>
       <c r="R7" t="n">
-        <v>7216579</v>
+        <v>7216566</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441206</v>
+        <v>113441236</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>91336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775841</v>
+        <v>775939</v>
       </c>
       <c r="R8" t="n">
-        <v>7216570</v>
+        <v>7216449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441200</v>
+        <v>113441334</v>
       </c>
       <c r="B9" t="n">
-        <v>91383</v>
+        <v>91356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775838</v>
+        <v>775924</v>
       </c>
       <c r="R9" t="n">
-        <v>7216566</v>
+        <v>7216402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441314</v>
+        <v>113441377</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91344</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775933</v>
+        <v>775928</v>
       </c>
       <c r="R10" t="n">
-        <v>7216437</v>
+        <v>7216628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441320</v>
+        <v>113441196</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91330</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775972</v>
+        <v>775933</v>
       </c>
       <c r="R11" t="n">
-        <v>7216501</v>
+        <v>7216437</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441377</v>
+        <v>113441266</v>
       </c>
       <c r="B12" t="n">
-        <v>91340</v>
+        <v>91338</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775928</v>
+        <v>775948</v>
       </c>
       <c r="R12" t="n">
-        <v>7216628</v>
+        <v>7216449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441321</v>
+        <v>113441317</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>91387</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775964</v>
+        <v>776019</v>
       </c>
       <c r="R13" t="n">
-        <v>7216510</v>
+        <v>7216574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441334</v>
+        <v>113441367</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>88708</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775924</v>
+        <v>775936</v>
       </c>
       <c r="R14" t="n">
-        <v>7216402</v>
+        <v>7216436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441266</v>
+        <v>113441317</v>
       </c>
       <c r="B12" t="n">
-        <v>91338</v>
+        <v>91387</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775948</v>
+        <v>776019</v>
       </c>
       <c r="R12" t="n">
-        <v>7216449</v>
+        <v>7216574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441317</v>
+        <v>113441266</v>
       </c>
       <c r="B13" t="n">
-        <v>91387</v>
+        <v>91338</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776019</v>
+        <v>775948</v>
       </c>
       <c r="R13" t="n">
-        <v>7216574</v>
+        <v>7216449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441322</v>
+        <v>113441367</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>88714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775914</v>
+        <v>775936</v>
       </c>
       <c r="R2" t="n">
-        <v>7216634</v>
+        <v>7216436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441201</v>
+        <v>113441199</v>
       </c>
       <c r="B3" t="n">
-        <v>91388</v>
+        <v>91393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775880</v>
+        <v>776019</v>
       </c>
       <c r="R3" t="n">
-        <v>7216579</v>
+        <v>7216574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441320</v>
+        <v>113441323</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>91354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775972</v>
+        <v>775841</v>
       </c>
       <c r="R4" t="n">
-        <v>7216501</v>
+        <v>7216570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441323</v>
+        <v>113441216</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>91362</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775841</v>
+        <v>775924</v>
       </c>
       <c r="R5" t="n">
-        <v>7216570</v>
+        <v>7216402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441321</v>
+        <v>113441203</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775964</v>
+        <v>775972</v>
       </c>
       <c r="R6" t="n">
-        <v>7216510</v>
+        <v>7216501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>113441318</v>
       </c>
       <c r="B7" t="n">
-        <v>91387</v>
+        <v>91393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441236</v>
+        <v>113441196</v>
       </c>
       <c r="B8" t="n">
         <v>91336</v>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775939</v>
+        <v>775933</v>
       </c>
       <c r="R8" t="n">
-        <v>7216449</v>
+        <v>7216437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441334</v>
+        <v>113441258</v>
       </c>
       <c r="B9" t="n">
-        <v>91356</v>
+        <v>91350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775924</v>
+        <v>775928</v>
       </c>
       <c r="R9" t="n">
-        <v>7216402</v>
+        <v>7216628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441377</v>
+        <v>113441321</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>91354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775928</v>
+        <v>775964</v>
       </c>
       <c r="R10" t="n">
-        <v>7216628</v>
+        <v>7216510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441196</v>
+        <v>113441385</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>91344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775933</v>
+        <v>775948</v>
       </c>
       <c r="R11" t="n">
-        <v>7216437</v>
+        <v>7216449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441317</v>
+        <v>113441319</v>
       </c>
       <c r="B12" t="n">
-        <v>91387</v>
+        <v>91394</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776019</v>
+        <v>775880</v>
       </c>
       <c r="R12" t="n">
-        <v>7216574</v>
+        <v>7216579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441266</v>
+        <v>113441322</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>91354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775948</v>
+        <v>775914</v>
       </c>
       <c r="R13" t="n">
-        <v>7216449</v>
+        <v>7216634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441367</v>
+        <v>113441355</v>
       </c>
       <c r="B14" t="n">
-        <v>88708</v>
+        <v>91342</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775936</v>
+        <v>775939</v>
       </c>
       <c r="R14" t="n">
-        <v>7216436</v>
+        <v>7216449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441323</v>
+        <v>113441216</v>
       </c>
       <c r="B4" t="n">
-        <v>91354</v>
+        <v>91362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775841</v>
+        <v>775924</v>
       </c>
       <c r="R4" t="n">
-        <v>7216570</v>
+        <v>7216402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441216</v>
+        <v>113441323</v>
       </c>
       <c r="B5" t="n">
-        <v>91362</v>
+        <v>91354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775924</v>
+        <v>775841</v>
       </c>
       <c r="R5" t="n">
-        <v>7216402</v>
+        <v>7216570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441203</v>
+        <v>113441318</v>
       </c>
       <c r="B6" t="n">
-        <v>91354</v>
+        <v>91393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775972</v>
+        <v>775838</v>
       </c>
       <c r="R6" t="n">
-        <v>7216501</v>
+        <v>7216566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441318</v>
+        <v>113441203</v>
       </c>
       <c r="B7" t="n">
-        <v>91393</v>
+        <v>91354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775838</v>
+        <v>775972</v>
       </c>
       <c r="R7" t="n">
-        <v>7216566</v>
+        <v>7216501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441322</v>
+        <v>113441205</v>
       </c>
       <c r="B13" t="n">
         <v>91354</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441367</v>
+        <v>113441320</v>
       </c>
       <c r="B2" t="n">
-        <v>88714</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775936</v>
+        <v>775972</v>
       </c>
       <c r="R2" t="n">
-        <v>7216436</v>
+        <v>7216501</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441199</v>
+        <v>113441205</v>
       </c>
       <c r="B3" t="n">
-        <v>91393</v>
+        <v>91354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776019</v>
+        <v>775914</v>
       </c>
       <c r="R3" t="n">
-        <v>7216574</v>
+        <v>7216634</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441216</v>
+        <v>113441314</v>
       </c>
       <c r="B4" t="n">
-        <v>91362</v>
+        <v>91336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775924</v>
+        <v>775933</v>
       </c>
       <c r="R4" t="n">
-        <v>7216402</v>
+        <v>7216437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441323</v>
+        <v>113441317</v>
       </c>
       <c r="B5" t="n">
-        <v>91354</v>
+        <v>91393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775841</v>
+        <v>776019</v>
       </c>
       <c r="R5" t="n">
-        <v>7216570</v>
+        <v>7216574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441318</v>
+        <v>113441385</v>
       </c>
       <c r="B6" t="n">
-        <v>91393</v>
+        <v>91344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775838</v>
+        <v>775948</v>
       </c>
       <c r="R6" t="n">
-        <v>7216566</v>
+        <v>7216449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441203</v>
+        <v>113441236</v>
       </c>
       <c r="B7" t="n">
-        <v>91354</v>
+        <v>91342</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775972</v>
+        <v>775939</v>
       </c>
       <c r="R7" t="n">
-        <v>7216501</v>
+        <v>7216449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441196</v>
+        <v>113441200</v>
       </c>
       <c r="B8" t="n">
-        <v>91336</v>
+        <v>91393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775933</v>
+        <v>775838</v>
       </c>
       <c r="R8" t="n">
-        <v>7216437</v>
+        <v>7216566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441258</v>
+        <v>113441216</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91362</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775928</v>
+        <v>775924</v>
       </c>
       <c r="R9" t="n">
-        <v>7216628</v>
+        <v>7216402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441321</v>
+        <v>113441319</v>
       </c>
       <c r="B10" t="n">
-        <v>91354</v>
+        <v>91394</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775964</v>
+        <v>775880</v>
       </c>
       <c r="R10" t="n">
-        <v>7216510</v>
+        <v>7216579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441385</v>
+        <v>113441323</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775948</v>
+        <v>775841</v>
       </c>
       <c r="R11" t="n">
-        <v>7216449</v>
+        <v>7216570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441319</v>
+        <v>113441367</v>
       </c>
       <c r="B12" t="n">
-        <v>91394</v>
+        <v>88714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775880</v>
+        <v>775936</v>
       </c>
       <c r="R12" t="n">
-        <v>7216579</v>
+        <v>7216436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441205</v>
+        <v>113441258</v>
       </c>
       <c r="B13" t="n">
-        <v>91354</v>
+        <v>91350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775914</v>
+        <v>775928</v>
       </c>
       <c r="R13" t="n">
-        <v>7216634</v>
+        <v>7216628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441355</v>
+        <v>113441321</v>
       </c>
       <c r="B14" t="n">
-        <v>91342</v>
+        <v>91354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775939</v>
+        <v>775964</v>
       </c>
       <c r="R14" t="n">
-        <v>7216449</v>
+        <v>7216510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441320</v>
+        <v>113441321</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>91361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775972</v>
+        <v>775964</v>
       </c>
       <c r="R2" t="n">
-        <v>7216501</v>
+        <v>7216510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441205</v>
+        <v>113441318</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>91400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775914</v>
+        <v>775838</v>
       </c>
       <c r="R3" t="n">
-        <v>7216634</v>
+        <v>7216566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441314</v>
+        <v>113441323</v>
       </c>
       <c r="B4" t="n">
-        <v>91336</v>
+        <v>91361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775933</v>
+        <v>775841</v>
       </c>
       <c r="R4" t="n">
-        <v>7216437</v>
+        <v>7216570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441317</v>
+        <v>113441355</v>
       </c>
       <c r="B5" t="n">
-        <v>91393</v>
+        <v>91349</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>776019</v>
+        <v>775939</v>
       </c>
       <c r="R5" t="n">
-        <v>7216574</v>
+        <v>7216449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441385</v>
+        <v>113441203</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>91361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775948</v>
+        <v>775972</v>
       </c>
       <c r="R6" t="n">
-        <v>7216449</v>
+        <v>7216501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441236</v>
+        <v>113441314</v>
       </c>
       <c r="B7" t="n">
-        <v>91342</v>
+        <v>91343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775939</v>
+        <v>775933</v>
       </c>
       <c r="R7" t="n">
-        <v>7216449</v>
+        <v>7216437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441200</v>
+        <v>113441201</v>
       </c>
       <c r="B8" t="n">
-        <v>91393</v>
+        <v>91401</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775838</v>
+        <v>775880</v>
       </c>
       <c r="R8" t="n">
-        <v>7216566</v>
+        <v>7216579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441216</v>
+        <v>113441367</v>
       </c>
       <c r="B9" t="n">
-        <v>91362</v>
+        <v>88721</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775924</v>
+        <v>775936</v>
       </c>
       <c r="R9" t="n">
-        <v>7216402</v>
+        <v>7216436</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441319</v>
+        <v>113441322</v>
       </c>
       <c r="B10" t="n">
-        <v>91394</v>
+        <v>91361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775880</v>
+        <v>775914</v>
       </c>
       <c r="R10" t="n">
-        <v>7216579</v>
+        <v>7216634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441323</v>
+        <v>113441216</v>
       </c>
       <c r="B11" t="n">
-        <v>91354</v>
+        <v>91369</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775841</v>
+        <v>775924</v>
       </c>
       <c r="R11" t="n">
-        <v>7216570</v>
+        <v>7216402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441367</v>
+        <v>113441266</v>
       </c>
       <c r="B12" t="n">
-        <v>88714</v>
+        <v>91351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775936</v>
+        <v>775948</v>
       </c>
       <c r="R12" t="n">
-        <v>7216436</v>
+        <v>7216449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>113441258</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441321</v>
+        <v>113441317</v>
       </c>
       <c r="B14" t="n">
-        <v>91354</v>
+        <v>91400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775964</v>
+        <v>776019</v>
       </c>
       <c r="R14" t="n">
-        <v>7216510</v>
+        <v>7216574</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441203</v>
+        <v>113441314</v>
       </c>
       <c r="B6" t="n">
-        <v>91361</v>
+        <v>91343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775972</v>
+        <v>775933</v>
       </c>
       <c r="R6" t="n">
-        <v>7216501</v>
+        <v>7216437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441314</v>
+        <v>113441203</v>
       </c>
       <c r="B7" t="n">
-        <v>91343</v>
+        <v>91361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775933</v>
+        <v>775972</v>
       </c>
       <c r="R7" t="n">
-        <v>7216437</v>
+        <v>7216501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441321</v>
+        <v>113441355</v>
       </c>
       <c r="B2" t="n">
-        <v>91361</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775964</v>
+        <v>775939</v>
       </c>
       <c r="R2" t="n">
-        <v>7216510</v>
+        <v>7216449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441318</v>
+        <v>113441323</v>
       </c>
       <c r="B3" t="n">
-        <v>91400</v>
+        <v>91366</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775838</v>
+        <v>775841</v>
       </c>
       <c r="R3" t="n">
-        <v>7216566</v>
+        <v>7216570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441323</v>
+        <v>113441320</v>
       </c>
       <c r="B4" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775841</v>
+        <v>775972</v>
       </c>
       <c r="R4" t="n">
-        <v>7216570</v>
+        <v>7216501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441355</v>
+        <v>113441205</v>
       </c>
       <c r="B5" t="n">
-        <v>91349</v>
+        <v>91366</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775939</v>
+        <v>775914</v>
       </c>
       <c r="R5" t="n">
-        <v>7216449</v>
+        <v>7216634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441314</v>
+        <v>113441196</v>
       </c>
       <c r="B6" t="n">
-        <v>91343</v>
+        <v>91348</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441203</v>
+        <v>113441216</v>
       </c>
       <c r="B7" t="n">
-        <v>91361</v>
+        <v>91374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775972</v>
+        <v>775924</v>
       </c>
       <c r="R7" t="n">
-        <v>7216501</v>
+        <v>7216402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441201</v>
+        <v>113441266</v>
       </c>
       <c r="B8" t="n">
-        <v>91401</v>
+        <v>91356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775880</v>
+        <v>775948</v>
       </c>
       <c r="R8" t="n">
-        <v>7216579</v>
+        <v>7216449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441367</v>
+        <v>113441377</v>
       </c>
       <c r="B9" t="n">
-        <v>88721</v>
+        <v>91362</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775936</v>
+        <v>775928</v>
       </c>
       <c r="R9" t="n">
-        <v>7216436</v>
+        <v>7216628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441322</v>
+        <v>113441321</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775914</v>
+        <v>775964</v>
       </c>
       <c r="R10" t="n">
-        <v>7216634</v>
+        <v>7216510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441216</v>
+        <v>113441200</v>
       </c>
       <c r="B11" t="n">
-        <v>91369</v>
+        <v>91405</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775924</v>
+        <v>775838</v>
       </c>
       <c r="R11" t="n">
-        <v>7216402</v>
+        <v>7216566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441266</v>
+        <v>113441367</v>
       </c>
       <c r="B12" t="n">
-        <v>91351</v>
+        <v>88690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775948</v>
+        <v>775936</v>
       </c>
       <c r="R12" t="n">
-        <v>7216449</v>
+        <v>7216436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441258</v>
+        <v>113441201</v>
       </c>
       <c r="B13" t="n">
-        <v>91357</v>
+        <v>91406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775928</v>
+        <v>775880</v>
       </c>
       <c r="R13" t="n">
-        <v>7216628</v>
+        <v>7216579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
         <v>113441317</v>
       </c>
       <c r="B14" t="n">
-        <v>91400</v>
+        <v>91405</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441321</v>
+        <v>113441200</v>
       </c>
       <c r="B10" t="n">
-        <v>91366</v>
+        <v>91405</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775964</v>
+        <v>775838</v>
       </c>
       <c r="R10" t="n">
-        <v>7216510</v>
+        <v>7216566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441200</v>
+        <v>113441367</v>
       </c>
       <c r="B11" t="n">
-        <v>91405</v>
+        <v>88690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775838</v>
+        <v>775936</v>
       </c>
       <c r="R11" t="n">
-        <v>7216566</v>
+        <v>7216436</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441367</v>
+        <v>113441321</v>
       </c>
       <c r="B12" t="n">
-        <v>88690</v>
+        <v>91366</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,34 +1711,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775936</v>
+        <v>775964</v>
       </c>
       <c r="R12" t="n">
-        <v>7216436</v>
+        <v>7216510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441355</v>
+        <v>113441196</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>91376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775939</v>
+        <v>775933</v>
       </c>
       <c r="R2" t="n">
-        <v>7216449</v>
+        <v>7216437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441323</v>
+        <v>113441320</v>
       </c>
       <c r="B3" t="n">
-        <v>91366</v>
+        <v>91394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775841</v>
+        <v>775972</v>
       </c>
       <c r="R3" t="n">
-        <v>7216570</v>
+        <v>7216501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441320</v>
+        <v>113441201</v>
       </c>
       <c r="B4" t="n">
-        <v>91366</v>
+        <v>91434</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775972</v>
+        <v>775880</v>
       </c>
       <c r="R4" t="n">
-        <v>7216501</v>
+        <v>7216579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441205</v>
+        <v>113441266</v>
       </c>
       <c r="B5" t="n">
-        <v>91366</v>
+        <v>91384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775914</v>
+        <v>775948</v>
       </c>
       <c r="R5" t="n">
-        <v>7216634</v>
+        <v>7216449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441196</v>
+        <v>113441322</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91394</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775933</v>
+        <v>775914</v>
       </c>
       <c r="R6" t="n">
-        <v>7216437</v>
+        <v>7216634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441216</v>
+        <v>113441236</v>
       </c>
       <c r="B7" t="n">
-        <v>91374</v>
+        <v>91382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775924</v>
+        <v>775939</v>
       </c>
       <c r="R7" t="n">
-        <v>7216402</v>
+        <v>7216449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441266</v>
+        <v>113441199</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>91433</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775948</v>
+        <v>776019</v>
       </c>
       <c r="R8" t="n">
-        <v>7216449</v>
+        <v>7216574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441377</v>
+        <v>113441204</v>
       </c>
       <c r="B9" t="n">
-        <v>91362</v>
+        <v>91394</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775928</v>
+        <v>775964</v>
       </c>
       <c r="R9" t="n">
-        <v>7216628</v>
+        <v>7216510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441200</v>
+        <v>113441258</v>
       </c>
       <c r="B10" t="n">
-        <v>91405</v>
+        <v>91390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775838</v>
+        <v>775928</v>
       </c>
       <c r="R10" t="n">
-        <v>7216566</v>
+        <v>7216628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441367</v>
+        <v>113441334</v>
       </c>
       <c r="B11" t="n">
-        <v>88690</v>
+        <v>91402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775936</v>
+        <v>775924</v>
       </c>
       <c r="R11" t="n">
-        <v>7216436</v>
+        <v>7216402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441321</v>
+        <v>113441200</v>
       </c>
       <c r="B12" t="n">
-        <v>91366</v>
+        <v>91433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775964</v>
+        <v>775838</v>
       </c>
       <c r="R12" t="n">
-        <v>7216510</v>
+        <v>7216566</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441201</v>
+        <v>113441367</v>
       </c>
       <c r="B13" t="n">
-        <v>91406</v>
+        <v>88718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775880</v>
+        <v>775936</v>
       </c>
       <c r="R13" t="n">
-        <v>7216579</v>
+        <v>7216436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441317</v>
+        <v>113441323</v>
       </c>
       <c r="B14" t="n">
-        <v>91405</v>
+        <v>91394</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776019</v>
+        <v>775841</v>
       </c>
       <c r="R14" t="n">
-        <v>7216574</v>
+        <v>7216570</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441196</v>
+        <v>113441236</v>
       </c>
       <c r="B2" t="n">
-        <v>91376</v>
+        <v>91382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775933</v>
+        <v>775939</v>
       </c>
       <c r="R2" t="n">
-        <v>7216437</v>
+        <v>7216449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441320</v>
+        <v>113441196</v>
       </c>
       <c r="B3" t="n">
-        <v>91394</v>
+        <v>91376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775972</v>
+        <v>775933</v>
       </c>
       <c r="R3" t="n">
-        <v>7216501</v>
+        <v>7216437</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441201</v>
+        <v>113441319</v>
       </c>
       <c r="B4" t="n">
         <v>91434</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441266</v>
+        <v>113441321</v>
       </c>
       <c r="B5" t="n">
-        <v>91384</v>
+        <v>91394</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775948</v>
+        <v>775964</v>
       </c>
       <c r="R5" t="n">
-        <v>7216449</v>
+        <v>7216510</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441322</v>
+        <v>113441320</v>
       </c>
       <c r="B6" t="n">
         <v>91394</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775914</v>
+        <v>775972</v>
       </c>
       <c r="R6" t="n">
-        <v>7216634</v>
+        <v>7216501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441236</v>
+        <v>113441266</v>
       </c>
       <c r="B7" t="n">
-        <v>91382</v>
+        <v>91384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775939</v>
+        <v>775948</v>
       </c>
       <c r="R7" t="n">
         <v>7216449</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441199</v>
+        <v>113441323</v>
       </c>
       <c r="B8" t="n">
-        <v>91433</v>
+        <v>91394</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776019</v>
+        <v>775841</v>
       </c>
       <c r="R8" t="n">
-        <v>7216574</v>
+        <v>7216570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441204</v>
+        <v>113441199</v>
       </c>
       <c r="B9" t="n">
-        <v>91394</v>
+        <v>91433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>775964</v>
+        <v>776019</v>
       </c>
       <c r="R9" t="n">
-        <v>7216510</v>
+        <v>7216574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441258</v>
+        <v>113441334</v>
       </c>
       <c r="B10" t="n">
-        <v>91390</v>
+        <v>91402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775928</v>
+        <v>775924</v>
       </c>
       <c r="R10" t="n">
-        <v>7216628</v>
+        <v>7216402</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441334</v>
+        <v>113441205</v>
       </c>
       <c r="B11" t="n">
-        <v>91402</v>
+        <v>91394</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775924</v>
+        <v>775914</v>
       </c>
       <c r="R11" t="n">
-        <v>7216402</v>
+        <v>7216634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441200</v>
+        <v>113441318</v>
       </c>
       <c r="B12" t="n">
         <v>91433</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113441367</v>
+        <v>113441248</v>
       </c>
       <c r="B13" t="n">
         <v>88718</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113441323</v>
+        <v>113441377</v>
       </c>
       <c r="B14" t="n">
-        <v>91394</v>
+        <v>91390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775841</v>
+        <v>775928</v>
       </c>
       <c r="R14" t="n">
-        <v>7216570</v>
+        <v>7216628</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441236</v>
+        <v>113441323</v>
       </c>
       <c r="B2" t="n">
-        <v>91382</v>
+        <v>91398</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775939</v>
+        <v>775841</v>
       </c>
       <c r="R2" t="n">
-        <v>7216449</v>
+        <v>7216570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>113441196</v>
       </c>
       <c r="B3" t="n">
-        <v>91376</v>
+        <v>91380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441319</v>
+        <v>113441320</v>
       </c>
       <c r="B4" t="n">
-        <v>91434</v>
+        <v>91398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775880</v>
+        <v>775972</v>
       </c>
       <c r="R4" t="n">
-        <v>7216579</v>
+        <v>7216501</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441321</v>
+        <v>113441216</v>
       </c>
       <c r="B5" t="n">
-        <v>91394</v>
+        <v>91406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775964</v>
+        <v>775924</v>
       </c>
       <c r="R5" t="n">
-        <v>7216510</v>
+        <v>7216402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441320</v>
+        <v>113441322</v>
       </c>
       <c r="B6" t="n">
-        <v>91394</v>
+        <v>91398</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775972</v>
+        <v>775914</v>
       </c>
       <c r="R6" t="n">
-        <v>7216501</v>
+        <v>7216634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441266</v>
+        <v>113441317</v>
       </c>
       <c r="B7" t="n">
-        <v>91384</v>
+        <v>91437</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775948</v>
+        <v>776019</v>
       </c>
       <c r="R7" t="n">
-        <v>7216449</v>
+        <v>7216574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441323</v>
+        <v>113441201</v>
       </c>
       <c r="B8" t="n">
-        <v>91394</v>
+        <v>91438</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775841</v>
+        <v>775880</v>
       </c>
       <c r="R8" t="n">
-        <v>7216570</v>
+        <v>7216579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441199</v>
+        <v>113441200</v>
       </c>
       <c r="B9" t="n">
-        <v>91433</v>
+        <v>91437</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>776019</v>
+        <v>775838</v>
       </c>
       <c r="R9" t="n">
-        <v>7216574</v>
+        <v>7216566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441334</v>
+        <v>113441321</v>
       </c>
       <c r="B10" t="n">
-        <v>91402</v>
+        <v>91398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sverige, Vb</t>
+          <t>Källdal, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>775924</v>
+        <v>775964</v>
       </c>
       <c r="R10" t="n">
-        <v>7216402</v>
+        <v>7216510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113441205</v>
+        <v>113441266</v>
       </c>
       <c r="B11" t="n">
-        <v>91394</v>
+        <v>91388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källdal, Vb</t>
+          <t>Sverige, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775914</v>
+        <v>775948</v>
       </c>
       <c r="R11" t="n">
-        <v>7216634</v>
+        <v>7216449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113441318</v>
+        <v>113441236</v>
       </c>
       <c r="B12" t="n">
-        <v>91433</v>
+        <v>91386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775838</v>
+        <v>775939</v>
       </c>
       <c r="R12" t="n">
-        <v>7216566</v>
+        <v>7216449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>113441248</v>
       </c>
       <c r="B13" t="n">
-        <v>88718</v>
+        <v>88722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>113441377</v>
       </c>
       <c r="B14" t="n">
-        <v>91390</v>
+        <v>91394</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 17660-2023 artfynd.xlsx
+++ b/artfynd/A 17660-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
